--- a/public/Guia/Devengado-CuentasConceptos.xlsx
+++ b/public/Guia/Devengado-CuentasConceptos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E656F30-08DF-457C-942D-E9CDCADC877B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DC5B33-ACAD-4ADA-8DC2-740752C35948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="102">
   <si>
     <t>cuenta</t>
   </si>
@@ -282,6 +282,66 @@
   </si>
   <si>
     <t>VII.1.1 (OTROS INGRESOS Y BENEFICIOS)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>4.3.9.9.01.13</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.13</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>4.3.9.9.01.14</t>
+  </si>
+  <si>
+    <t>1.1.2.2.02.14</t>
+  </si>
+  <si>
+    <t>Por el devengado al realizarse de otros ingresos propios derivados de Comisiones por retención en prestaciones , incluye Impuesto al Valor Agregado. 1 y 2</t>
   </si>
 </sst>
 </file>
@@ -311,12 +371,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -331,9 +397,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,12 +716,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A46DBC-EF38-4A4C-B82B-A7E0178DC86F}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="123" customWidth="1"/>
+    <col min="3" max="3" width="151.5703125" customWidth="1"/>
     <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1652,6 +1720,250 @@
         <v>5</v>
       </c>
     </row>
+    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/Guia/Devengado-CuentasConceptos.xlsx
+++ b/public/Guia/Devengado-CuentasConceptos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DC5B33-ACAD-4ADA-8DC2-740752C35948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79412DC-D3E7-4C51-9699-AEF19A80795F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -284,61 +284,61 @@
     <t>VII.1.1 (OTROS INGRESOS Y BENEFICIOS)</t>
   </si>
   <si>
-    <t>8.1.4.4.3.9.9.01.13</t>
-  </si>
-  <si>
-    <t>8.1.2.4.3.9.9.01.13</t>
-  </si>
-  <si>
-    <t>4.3.9.9.01.13</t>
+    <t>8.1.4.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.18</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>8.1.2.4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>4.2.1.2.01.19</t>
+  </si>
+  <si>
+    <t>1.1.2.2.04.03</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
+  </si>
+  <si>
+    <t>8.1.4.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>8.1.2.4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>4.3.1.9.01.02</t>
+  </si>
+  <si>
+    <t>1.1.2.9.02</t>
+  </si>
+  <si>
+    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
+  </si>
+  <si>
+    <t>8.1.4.4.1.7.1.02.02</t>
+  </si>
+  <si>
+    <t>8.1.2.4.1.7.1.02.02</t>
+  </si>
+  <si>
+    <t>4.1.7.1.02.02</t>
   </si>
   <si>
     <t>1.1.2.2.02.13</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por compensación bancaria de recursos propios</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>8.1.2.4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>4.2.1.2.01.18</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.02</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por Rendimientos por cuenta productiva de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.4.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>8.1.2.4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>4.2.1.2.01.19</t>
-  </si>
-  <si>
-    <t>1.1.2.2.04.03</t>
-  </si>
-  <si>
-    <t>Por el devengado de ingresos por Compensación bancaria de recursos del Fondo de Aportaciones para el Fortalecimiento de las Entidades Federativas (FAFEF)</t>
-  </si>
-  <si>
-    <t>8.1.4.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>8.1.2.4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>4.3.9.9.01.14</t>
-  </si>
-  <si>
-    <t>1.1.2.2.02.14</t>
   </si>
   <si>
     <t>Por el devengado al realizarse de otros ingresos propios derivados de Comisiones por retención en prestaciones , incluye Impuesto al Valor Agregado. 1 y 2</t>
@@ -371,18 +371,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -397,11 +391,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -716,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A46DBC-EF38-4A4C-B82B-A7E0178DC86F}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
@@ -1720,249 +1712,243 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>82</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="B72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>83</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="B73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" t="s">
         <v>86</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="A74" t="s">
         <v>84</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" t="s">
         <v>86</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="A75" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
         <v>86</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="A76" t="s">
         <v>87</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" t="s">
         <v>91</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="A77" t="s">
         <v>88</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="A78" t="s">
         <v>89</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="B78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" t="s">
         <v>91</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="A80" t="s">
         <v>92</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" t="s">
         <v>96</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="A81" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
         <v>96</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+      <c r="A82" t="s">
         <v>94</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" s="3" t="s">
+      <c r="B82" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" t="s">
         <v>95</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C83" s="3" t="s">
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
         <v>96</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+      <c r="A84" t="s">
         <v>97</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="B84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" t="s">
         <v>101</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+      <c r="A85" t="s">
         <v>98</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
         <v>101</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+      <c r="A86" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C86" s="3" t="s">
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" t="s">
         <v>101</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="A87" t="s">
         <v>50</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" s="3" t="s">
+      <c r="B87" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+      <c r="A88" t="s">
         <v>100</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
         <v>101</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
